--- a/artfynd/A 46659-2022 artfynd.xlsx
+++ b/artfynd/A 46659-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46659-2022 artfynd.xlsx
+++ b/artfynd/A 46659-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104342409</v>
+        <v>104342428</v>
       </c>
       <c r="B2" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,21 +710,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538405.635754399</v>
+        <v>538204</v>
       </c>
       <c r="R2" t="n">
-        <v>6599085.354605252</v>
+        <v>6598631</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,28 +752,17 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,50 +781,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104342418</v>
+        <v>104342429</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538394.4688617873</v>
+        <v>538284</v>
       </c>
       <c r="R3" t="n">
-        <v>6598835.118469413</v>
+        <v>6598652</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +858,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104342412</v>
+        <v>104342447</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,7 +922,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -960,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538474.3826841692</v>
+        <v>538450</v>
       </c>
       <c r="R4" t="n">
-        <v>6599022.133186463</v>
+        <v>6598599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,19 +964,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104342408</v>
+        <v>104342409</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538385.4952057763</v>
+        <v>538405</v>
       </c>
       <c r="R5" t="n">
-        <v>6599017.166095866</v>
+        <v>6599085</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,19 +1072,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,37 +1102,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104342423</v>
+        <v>104342413</v>
       </c>
       <c r="B6" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1205,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538315.1016220738</v>
+        <v>538494</v>
       </c>
       <c r="R6" t="n">
-        <v>6598793.212337617</v>
+        <v>6598941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,19 +1179,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,50 +1208,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104342416</v>
+        <v>104342452</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538404.6015848945</v>
+        <v>538491</v>
       </c>
       <c r="R7" t="n">
-        <v>6598838.266113184</v>
+        <v>6598653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,19 +1285,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,37 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104342428</v>
+        <v>104342455</v>
       </c>
       <c r="B8" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1429,7 +1349,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1438,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538203.9208885311</v>
+        <v>538519</v>
       </c>
       <c r="R8" t="n">
-        <v>6598630.734462917</v>
+        <v>6598710</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,19 +1391,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,37 +1420,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104342447</v>
+        <v>104588735</v>
       </c>
       <c r="B9" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>1079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1559,13 +1464,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538450.2509860381</v>
+        <v>538547</v>
       </c>
       <c r="R9" t="n">
-        <v>6598598.741965722</v>
+        <v>6598706</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,21 +1497,11 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1615,6 +1510,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1631,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104342449</v>
+        <v>104588736</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1671,7 +1566,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1680,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538457.3142219841</v>
+        <v>538504</v>
       </c>
       <c r="R10" t="n">
-        <v>6598603.888136653</v>
+        <v>6598986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,21 +1608,11 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1736,6 +1621,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1752,15 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104342452</v>
+        <v>104342407</v>
       </c>
       <c r="B11" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1795,16 +1680,18 @@
           <t>mycel</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538490.8718088751</v>
+        <v>538549</v>
       </c>
       <c r="R11" t="n">
-        <v>6598652.433656109</v>
+        <v>6598960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1834,27 +1721,18 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1873,15 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104342407</v>
+        <v>104342408</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538548.7114382247</v>
+        <v>538385</v>
       </c>
       <c r="R12" t="n">
-        <v>6598959.983818953</v>
+        <v>6599017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1957,19 +1830,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,15 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104342413</v>
+        <v>104342410</v>
       </c>
       <c r="B13" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2040,16 +1898,18 @@
           <t>mycel</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538494.0156306603</v>
+        <v>538412</v>
       </c>
       <c r="R13" t="n">
-        <v>6598941.158988902</v>
+        <v>6599121</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,27 +1939,18 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2118,15 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104342410</v>
+        <v>104342412</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,18 +2007,16 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538411.8738822985</v>
+        <v>538474</v>
       </c>
       <c r="R14" t="n">
-        <v>6599121.438600127</v>
+        <v>6599022</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,28 +2046,17 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2242,50 +2075,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104342420</v>
+        <v>104342423</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538364.5063308739</v>
+        <v>538315</v>
       </c>
       <c r="R15" t="n">
-        <v>6598832.783236567</v>
+        <v>6598793</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2315,19 +2152,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2354,37 +2181,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104342429</v>
+        <v>111945964</v>
       </c>
       <c r="B16" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>1593</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2394,7 +2216,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2403,10 +2225,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538283.504521252</v>
+        <v>538439</v>
       </c>
       <c r="R16" t="n">
-        <v>6598651.839287194</v>
+        <v>6598902</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,22 +2255,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,6 +2271,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2475,37 +2292,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104342455</v>
+        <v>111945963</v>
       </c>
       <c r="B17" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>366</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2524,13 +2336,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538518.7498990654</v>
+        <v>538477</v>
       </c>
       <c r="R17" t="n">
-        <v>6598709.546188025</v>
+        <v>6598834</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2554,22 +2366,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2580,6 +2382,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2596,50 +2403,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104342426</v>
+        <v>104342449</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538205.4435399838</v>
+        <v>538457</v>
       </c>
       <c r="R18" t="n">
-        <v>6598680.981278611</v>
+        <v>6598604</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2669,19 +2480,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2708,50 +2509,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104342427</v>
+        <v>104588734</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538193.4113400322</v>
+        <v>538465</v>
       </c>
       <c r="R19" t="n">
-        <v>6598664.622747406</v>
+        <v>6598518</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2781,21 +2586,11 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2804,6 +2599,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2820,37 +2620,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104588736</v>
+        <v>104588737</v>
       </c>
       <c r="B20" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1079</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2860,7 +2655,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2869,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538504.7436038165</v>
+        <v>538533</v>
       </c>
       <c r="R20" t="n">
-        <v>6598985.40800613</v>
+        <v>6598989</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2902,19 +2697,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2946,62 +2731,52 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104588735</v>
+        <v>104342464</v>
       </c>
       <c r="B21" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1079</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538547.2459107963</v>
+        <v>538550</v>
       </c>
       <c r="R21" t="n">
-        <v>6598706.286478708</v>
+        <v>6598956</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3028,21 +2803,11 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3051,11 +2816,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>Michael Andersson</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3072,59 +2832,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104588737</v>
+        <v>104342457</v>
       </c>
       <c r="B22" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>103001</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538533.6781099818</v>
+        <v>538568</v>
       </c>
       <c r="R22" t="n">
-        <v>6598988.748446089</v>
+        <v>6598691</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3154,21 +2900,11 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3177,11 +2913,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>Michael Andersson</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3198,57 +2929,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104342464</v>
+        <v>104342416</v>
       </c>
       <c r="B23" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538550</v>
+        <v>538404</v>
       </c>
       <c r="R23" t="n">
-        <v>6598956</v>
+        <v>6598839</v>
       </c>
       <c r="S23" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3304,37 +3026,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104342457</v>
+        <v>104342418</v>
       </c>
       <c r="B24" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3344,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538568</v>
+        <v>538395</v>
       </c>
       <c r="R24" t="n">
-        <v>6598691</v>
+        <v>6598835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3406,15 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111945961</v>
+        <v>104342420</v>
       </c>
       <c r="B25" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3439,26 +3151,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538409</v>
+        <v>538365</v>
       </c>
       <c r="R25" t="n">
-        <v>6598847</v>
+        <v>6598833</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3485,12 +3188,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3501,11 +3204,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3522,62 +3220,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111945963</v>
+        <v>104342426</v>
       </c>
       <c r="B26" t="n">
-        <v>89950</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538477</v>
+        <v>538205</v>
       </c>
       <c r="R26" t="n">
-        <v>6598834</v>
+        <v>6598681</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3601,12 +3285,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3617,11 +3301,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3638,15 +3317,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111945964</v>
+        <v>104342427</v>
       </c>
       <c r="B27" t="n">
-        <v>88140</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3654,43 +3328,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1593</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Norrbyhammar, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538439</v>
+        <v>538194</v>
       </c>
       <c r="R27" t="n">
-        <v>6598902</v>
+        <v>6598665</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3717,12 +3382,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3733,11 +3398,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3751,6 +3411,223 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>111945961</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Norrbyhammar, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>538408</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6598847</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131307664</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norrbyhammar, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>538394</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6598835</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>T-Lin-0037</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46659-2022 artfynd.xlsx
+++ b/artfynd/A 46659-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342428</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342429</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342447</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342409</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342413</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342452</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342455</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104588736</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342408</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1746,6 +1796,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342410</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1852,6 +1907,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342412</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1958,6 +2018,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342423</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2069,6 +2134,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111945964</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2180,6 +2250,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111945963</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2286,6 +2361,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342449</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2397,6 +2477,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104588734</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2508,6 +2593,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104588737</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2605,6 +2695,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342416</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2702,6 +2797,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342418</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2799,6 +2899,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342420</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2896,6 +3001,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342426</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2993,6 +3103,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342427</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3104,6 +3219,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111945961</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3210,6 +3330,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131307664</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3321,6 +3446,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104588735</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3430,6 +3560,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342407</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3531,6 +3666,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342464</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3628,8 +3768,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342457</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>